--- a/assets/constructions/examples/ctd_eths_arborholder.xlsx
+++ b/assets/constructions/examples/ctd_eths_arborholder.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,11 +559,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E4-40ER25</t>
+          <t>E4-50ER40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -579,7 +599,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DIN_69880_1:VDI40</t>
+          <t>DIN_69880_1:VDI50</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -592,12 +612,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ER25</t>
+          <t>ER40</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ER25</t>
+          <t>ER40</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -614,16 +634,16 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="N2" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="O2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -632,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
@@ -647,11 +667,17 @@
           <t>2022/LIKON Инструментальный каталог</t>
         </is>
       </c>
+      <c r="AA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E4-25ER25</t>
+          <t>E4-40ER40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -667,7 +693,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DIN_69880_1:VDI25</t>
+          <t>DIN_69880_1:VDI40</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -680,12 +706,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ER25</t>
+          <t>ER40</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ER25</t>
+          <t>ER40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -702,16 +728,16 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="N3" t="n">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="O3" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="P3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
@@ -720,7 +746,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
@@ -735,11 +761,17 @@
           <t>2022/LIKON Инструментальный каталог</t>
         </is>
       </c>
+      <c r="AA3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E4-60ER40</t>
+          <t>E4-30ER32</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -755,7 +787,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DIN_69880_1:VDI60</t>
+          <t>DIN_69880_1:VDI30</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -768,12 +800,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ER40</t>
+          <t>ER32</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ER40</t>
+          <t>ER32</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -790,16 +822,16 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="N4" t="n">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="O4" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -808,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
@@ -823,19 +855,29 @@
           <t>2022/LIKON Инструментальный каталог</t>
         </is>
       </c>
+      <c r="AA4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E4-16ER20</t>
+          <t>E4-20x32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LIKON</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>BISON</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VDI-ER HOLDERS</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>DIN 69880</t>
@@ -843,7 +885,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DIN_69880_1:VDI16</t>
+          <t>DIN_69880_1:VDI20</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -856,17 +898,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ER20</t>
+          <t>ER32</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ER20</t>
+          <t>ER32</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>LIKON</t>
+          <t>ISO</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -875,19 +917,17 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="N5" t="n">
-        <v>40</v>
-      </c>
-      <c r="O5" t="n">
-        <v>16</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -896,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
@@ -908,14 +948,20 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2022/LIKON Инструментальный каталог</t>
-        </is>
-      </c>
+          <t>2020 / BISON Catalog</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E4-16ER16</t>
+          <t>E4-16ER20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -944,12 +990,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ER16</t>
+          <t>ER20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ER16</t>
+          <t>ER20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -966,7 +1012,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="N6" t="n">
         <v>40</v>
@@ -975,7 +1021,7 @@
         <v>16</v>
       </c>
       <c r="P6" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -984,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
@@ -999,6 +1045,12 @@
           <t>2022/LIKON Инструментальный каталог</t>
         </is>
       </c>
+      <c r="AA6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
